--- a/dirasakan_bulanan_wilpgr.xlsx
+++ b/dirasakan_bulanan_wilpgr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AC98A0-4267-4196-AE2A-1E3CC746146D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BECF63-A57F-4BDE-BFE5-A8FB682B6E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Tanggal</t>
   </si>
@@ -91,17 +91,28 @@
   </si>
   <si>
     <t>dirasakan di wilayah Kab. Sumbawa Barat, Kab. Sumbawa, Kab. Bima, dan Kab. Lombok Timur II MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kuta dan Kuta Selatan II MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di daerah Kodi Sumba Barat Daya I-II MMI</t>
+  </si>
+  <si>
+    <t>84 km BaratDaya Kota Denpasar-Bali</t>
+  </si>
+  <si>
+    <t>South of Sumbawa, Indonesia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -132,17 +143,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,11 +467,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
@@ -470,194 +480,213 @@
     <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>46054</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5">
         <v>0.85359953703703706</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>-8.49</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>115.66</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>9</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>3.5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>46068</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.86398148148148146</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-11.37</v>
+      </c>
+      <c r="D3" s="2">
+        <v>118.04</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>46069</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B4" s="5">
         <v>0.77935185185185185</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="2">
         <v>-8.6</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="2">
         <v>118.41</v>
       </c>
-      <c r="E3">
+      <c r="E4" s="2">
         <v>114</v>
       </c>
-      <c r="F3">
+      <c r="F4" s="2">
         <v>3.6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46070</v>
+      </c>
+      <c r="B5" s="5">
+        <v>9.9652777777777785E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-9.2272999999999996</v>
+      </c>
+      <c r="D5" s="2">
+        <v>114.69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>84.2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>46071</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B6" s="5">
         <v>9.9432870370370366E-2</v>
       </c>
-      <c r="C4">
+      <c r="C6" s="2">
         <v>-8.2200000000000006</v>
       </c>
-      <c r="D4">
+      <c r="D6" s="2">
         <v>116.39</v>
       </c>
-      <c r="E4">
+      <c r="E6" s="2">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F6" s="2">
         <v>3.5</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>46076</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B7" s="5">
         <v>0.77505787037037033</v>
       </c>
-      <c r="C5">
+      <c r="C7" s="2">
         <v>-9.26</v>
       </c>
-      <c r="D5">
+      <c r="D7" s="2">
         <v>115.65</v>
       </c>
-      <c r="E5">
+      <c r="E7" s="2">
         <v>44</v>
       </c>
-      <c r="F5">
+      <c r="F7" s="2">
         <v>4</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>46081</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B8" s="5">
         <v>9.824074074074074E-2</v>
       </c>
-      <c r="C6">
+      <c r="C8" s="2">
         <v>-7.79</v>
       </c>
-      <c r="D6">
+      <c r="D8" s="2">
         <v>117.35</v>
       </c>
-      <c r="E6">
+      <c r="E8" s="2">
         <v>18</v>
       </c>
-      <c r="F6">
+      <c r="F8" s="2">
         <v>4.7</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/dirasakan_bulanan_wilpgr.xlsx
+++ b/dirasakan_bulanan_wilpgr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BECF63-A57F-4BDE-BFE5-A8FB682B6E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EA5607-5A0C-45DD-A1E1-B59F3B297C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Tanggal</t>
   </si>
@@ -63,62 +63,59 @@
     <t>Dirasakan</t>
   </si>
   <si>
-    <t>22 km Tenggara Karangasem-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Karangasem III MMI</t>
-  </si>
-  <si>
-    <t>9 km Barat Daya Dompu-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Sumbawa Besar III MMI, Kota Bima II MMI</t>
-  </si>
-  <si>
-    <t>29 km Timur Laut Lombok Utara-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Lombok Timur II-III MMI</t>
-  </si>
-  <si>
-    <t>70 km Tenggara Kuta Selatan-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kuta, Kuta Selatan, Klungkung, Lombok Barat, dan Lombok Tengah II MMI</t>
-  </si>
-  <si>
-    <t>78 km Utara Sumbawa-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Sumbawa Barat, Kab. Sumbawa, Kab. Bima, dan Kab. Lombok Timur II MMI</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kuta dan Kuta Selatan II MMI</t>
-  </si>
-  <si>
-    <t>dirasakan di daerah Kodi Sumba Barat Daya I-II MMI</t>
-  </si>
-  <si>
-    <t>84 km BaratDaya Kota Denpasar-Bali</t>
-  </si>
-  <si>
-    <t>South of Sumbawa, Indonesia</t>
+    <t>63 km Tenggara Kuta Selatan-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kota Denpasar, Kab. Badung, Kab. Lombok Tengah, Kab. Lombok Barat, Kota Mataram III MMI, Kab. Tabanan, Kab. Gianyar, Kab. Lombok Timur, Kab. Sumbawa, Kab. Sumbawa Barat II MMI</t>
+  </si>
+  <si>
+    <t>23 km Tenggara Karangasem-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Karangasem II - III MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Karangasem II MMI</t>
+  </si>
+  <si>
+    <t>21 km Barat Kabupaten Sumbawa-NTB</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kab. Sumbawa II MMI</t>
+  </si>
+  <si>
+    <t>103 km BaratDaya Dompu-NTB</t>
+  </si>
+  <si>
+    <t>dirasakan di wiliayah Sumbawa dan Bima III MMI</t>
+  </si>
+  <si>
+    <t>Datetime (WIB)</t>
+  </si>
+  <si>
+    <t>Datetime (UTC)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -143,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -151,8 +148,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,225 +468,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="159" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B2" s="5">
-        <v>0.85359953703703706</v>
-      </c>
-      <c r="C2" s="2">
-        <v>-8.49</v>
-      </c>
-      <c r="D2" s="2">
-        <v>115.66</v>
+        <v>0.4533564814814815</v>
+      </c>
+      <c r="C2" s="10">
+        <f>A2+B2</f>
+        <v>46082.453356481485</v>
+      </c>
+      <c r="D2" s="10">
+        <f>C2-(7/24)</f>
+        <v>46082.16168981482</v>
       </c>
       <c r="E2" s="2">
+        <v>-9.27</v>
+      </c>
+      <c r="F2" s="2">
+        <v>115.53</v>
+      </c>
+      <c r="G2" s="2">
+        <v>75</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.33109953703703704</v>
+      </c>
+      <c r="C3" s="10">
+        <f t="shared" ref="C3:C6" si="0">A3+B3</f>
+        <v>46092.331099537034</v>
+      </c>
+      <c r="D3" s="10">
+        <f t="shared" ref="D3:D6" si="1">C3-(7/24)</f>
+        <v>46092.03943287037</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-8.5299999999999994</v>
+      </c>
+      <c r="F3" s="2">
+        <v>117.24</v>
+      </c>
+      <c r="G3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="8">
         <v>3.5</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
+      <c r="I3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46068</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.86398148148148146</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-11.37</v>
-      </c>
-      <c r="D3" s="2">
-        <v>118.04</v>
-      </c>
-      <c r="E3" s="2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>46097</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.77915509259259264</v>
+      </c>
+      <c r="C4" s="10">
+        <f t="shared" si="0"/>
+        <v>46097.77915509259</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" si="1"/>
+        <v>46097.487488425926</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-9.42</v>
+      </c>
+      <c r="F4" s="2">
+        <v>118.18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>28</v>
+      </c>
+      <c r="H4" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46104</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.47204861111111113</v>
+      </c>
+      <c r="C5" s="10">
+        <f t="shared" si="0"/>
+        <v>46104.472048611111</v>
+      </c>
+      <c r="D5" s="10">
+        <f t="shared" si="1"/>
+        <v>46104.180381944447</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-8.4700000000000006</v>
+      </c>
+      <c r="F5" s="2">
+        <v>115.69</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
+      <c r="J5" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>46069</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.77935185185185185</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-8.6</v>
-      </c>
-      <c r="D4" s="2">
-        <v>118.41</v>
-      </c>
-      <c r="E4" s="2">
-        <v>114</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="G4" s="2" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.59361111111111109</v>
+      </c>
+      <c r="C6" s="10">
+        <f t="shared" si="0"/>
+        <v>46107.593611111108</v>
+      </c>
+      <c r="D6" s="10">
+        <f t="shared" si="1"/>
+        <v>46107.301944444444</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-8.4700000000000006</v>
+      </c>
+      <c r="F6" s="2">
+        <v>115.69</v>
+      </c>
+      <c r="G6" s="2">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>46070</v>
-      </c>
-      <c r="B5" s="5">
-        <v>9.9652777777777785E-2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>-9.2272999999999996</v>
-      </c>
-      <c r="D5" s="2">
-        <v>114.69</v>
-      </c>
-      <c r="E5" s="2">
-        <v>84.2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>4</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>46071</v>
-      </c>
-      <c r="B6" s="5">
-        <v>9.9432870370370366E-2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-8.2200000000000006</v>
-      </c>
-      <c r="D6" s="2">
-        <v>116.39</v>
-      </c>
-      <c r="E6" s="2">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>46076</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.77505787037037033</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-9.26</v>
-      </c>
-      <c r="D7" s="2">
-        <v>115.65</v>
-      </c>
-      <c r="E7" s="2">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>46081</v>
-      </c>
-      <c r="B8" s="5">
-        <v>9.824074074074074E-2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-7.79</v>
-      </c>
-      <c r="D8" s="2">
-        <v>117.35</v>
-      </c>
-      <c r="E8" s="2">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2">
-        <v>4.7</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/dirasakan_bulanan_wilpgr.xlsx
+++ b/dirasakan_bulanan_wilpgr.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EA5607-5A0C-45DD-A1E1-B59F3B297C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B3AC59-A7AD-4DB2-8E0A-5A3130C0860B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Tanggal</t>
   </si>
@@ -63,37 +60,46 @@
     <t>Dirasakan</t>
   </si>
   <si>
-    <t>63 km Tenggara Kuta Selatan-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kota Denpasar, Kab. Badung, Kab. Lombok Tengah, Kab. Lombok Barat, Kota Mataram III MMI, Kab. Tabanan, Kab. Gianyar, Kab. Lombok Timur, Kab. Sumbawa, Kab. Sumbawa Barat II MMI</t>
-  </si>
-  <si>
-    <t>23 km Tenggara Karangasem-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Karangasem II - III MMI</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Karangasem II MMI</t>
-  </si>
-  <si>
-    <t>21 km Barat Kabupaten Sumbawa-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Sumbawa II MMI</t>
-  </si>
-  <si>
-    <t>103 km BaratDaya Dompu-NTB</t>
-  </si>
-  <si>
-    <t>dirasakan di wiliayah Sumbawa dan Bima III MMI</t>
-  </si>
-  <si>
-    <t>Datetime (WIB)</t>
-  </si>
-  <si>
-    <t>Datetime (UTC)</t>
+    <t>22 km Tenggara Karangasem-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kab. Karangasem III MMI</t>
+  </si>
+  <si>
+    <t>9 km Barat Daya Dompu-NTB</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Sumbawa Besar III MMI, Kota Bima II MMI</t>
+  </si>
+  <si>
+    <t>29 km Timur Laut Lombok Utara-NTB</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Lombok Timur II-III MMI</t>
+  </si>
+  <si>
+    <t>70 km Tenggara Kuta Selatan-Bali</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kuta, Kuta Selatan, Klungkung, Lombok Barat, dan Lombok Tengah II MMI</t>
+  </si>
+  <si>
+    <t>78 km Utara Sumbawa-NTB</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kab. Sumbawa Barat, Kab. Sumbawa, Kab. Bima, dan Kab. Lombok Timur II MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di wilayah Kuta dan Kuta Selatan II MMI</t>
+  </si>
+  <si>
+    <t>dirasakan di daerah Kodi Sumba Barat Daya I-II MMI</t>
+  </si>
+  <si>
+    <t>84 km BaratDaya Kota Denpasar-Bali</t>
+  </si>
+  <si>
+    <t>South of Sumbawa, Indonesia</t>
   </si>
 </sst>
 </file>
@@ -101,21 +107,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -140,20 +141,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,221 +462,225 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.77734375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="159" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.85359953703703706</v>
+      </c>
+      <c r="C2">
+        <v>-8.49</v>
+      </c>
+      <c r="D2">
+        <v>115.66</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>3.5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
+        <v>46068</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.86398148148148146</v>
+      </c>
+      <c r="C3">
+        <v>-11.37</v>
+      </c>
+      <c r="D3">
+        <v>118.04</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.77935185185185185</v>
+      </c>
+      <c r="C4">
+        <v>-8.6</v>
+      </c>
+      <c r="D4">
+        <v>118.41</v>
+      </c>
+      <c r="E4">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>3.6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>46070</v>
+      </c>
+      <c r="B5" s="3">
+        <v>9.9652777777777785E-2</v>
+      </c>
+      <c r="C5">
+        <v>-9.2272999999999996</v>
+      </c>
+      <c r="D5">
+        <v>114.69</v>
+      </c>
+      <c r="E5">
+        <v>84.2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
+        <v>46071</v>
+      </c>
+      <c r="B6" s="3">
+        <v>9.9432870370370366E-2</v>
+      </c>
+      <c r="C6">
+        <v>-8.2200000000000006</v>
+      </c>
+      <c r="D6">
+        <v>116.39</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.77505787037037033</v>
+      </c>
+      <c r="C7">
+        <v>-9.26</v>
+      </c>
+      <c r="D7">
+        <v>115.65</v>
+      </c>
+      <c r="E7">
+        <v>44</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9.824074074074074E-2</v>
+      </c>
+      <c r="C8">
+        <v>-7.79</v>
+      </c>
+      <c r="D8">
+        <v>117.35</v>
+      </c>
+      <c r="E8">
+        <v>18</v>
+      </c>
+      <c r="F8">
+        <v>4.7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>46082</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.4533564814814815</v>
-      </c>
-      <c r="C2" s="10">
-        <f>A2+B2</f>
-        <v>46082.453356481485</v>
-      </c>
-      <c r="D2" s="10">
-        <f>C2-(7/24)</f>
-        <v>46082.16168981482</v>
-      </c>
-      <c r="E2" s="2">
-        <v>-9.27</v>
-      </c>
-      <c r="F2" s="2">
-        <v>115.53</v>
-      </c>
-      <c r="G2" s="2">
-        <v>75</v>
-      </c>
-      <c r="H2" s="2">
-        <v>4.7</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46092</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.33109953703703704</v>
-      </c>
-      <c r="C3" s="10">
-        <f t="shared" ref="C3:C6" si="0">A3+B3</f>
-        <v>46092.331099537034</v>
-      </c>
-      <c r="D3" s="10">
-        <f t="shared" ref="D3:D6" si="1">C3-(7/24)</f>
-        <v>46092.03943287037</v>
-      </c>
-      <c r="E3" s="2">
-        <v>-8.5299999999999994</v>
-      </c>
-      <c r="F3" s="2">
-        <v>117.24</v>
-      </c>
-      <c r="G3" s="2">
-        <v>10</v>
-      </c>
-      <c r="H3" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>46097</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.77915509259259264</v>
-      </c>
-      <c r="C4" s="10">
-        <f t="shared" si="0"/>
-        <v>46097.77915509259</v>
-      </c>
-      <c r="D4" s="10">
-        <f t="shared" si="1"/>
-        <v>46097.487488425926</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-9.42</v>
-      </c>
-      <c r="F4" s="2">
-        <v>118.18</v>
-      </c>
-      <c r="G4" s="2">
-        <v>28</v>
-      </c>
-      <c r="H4" s="8">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>46104</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.47204861111111113</v>
-      </c>
-      <c r="C5" s="10">
-        <f t="shared" si="0"/>
-        <v>46104.472048611111</v>
-      </c>
-      <c r="D5" s="10">
-        <f t="shared" si="1"/>
-        <v>46104.180381944447</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-8.4700000000000006</v>
-      </c>
-      <c r="F5" s="2">
-        <v>115.69</v>
-      </c>
-      <c r="G5" s="2">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>46107</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.59361111111111109</v>
-      </c>
-      <c r="C6" s="10">
-        <f t="shared" si="0"/>
-        <v>46107.593611111108</v>
-      </c>
-      <c r="D6" s="10">
-        <f t="shared" si="1"/>
-        <v>46107.301944444444</v>
-      </c>
-      <c r="E6" s="2">
-        <v>-8.4700000000000006</v>
-      </c>
-      <c r="F6" s="2">
-        <v>115.69</v>
-      </c>
-      <c r="G6" s="2">
-        <v>14</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
